--- a/gte/nodes/LPC/compressor_blade_strength.xlsx
+++ b/gte/nodes/LPC/compressor_blade_strength.xlsx
@@ -1195,43 +1195,43 @@
         <v>46286804509126.195</v>
       </c>
       <c r="F3">
-        <v>282.06518102315437</v>
+        <v>282.06518102315431</v>
       </c>
       <c r="G3">
-        <v>36.296650963442083</v>
+        <v>27.222488222581564</v>
       </c>
       <c r="H3">
         <v>13299304.169079844</v>
       </c>
       <c r="I3">
-        <v>47149754963864.609</v>
+        <v>47149754963864.617</v>
       </c>
       <c r="J3">
-        <v>97.126137383957371</v>
+        <v>95.2781125187441</v>
       </c>
       <c r="K3">
         <v>105.89248712718322</v>
       </c>
       <c r="L3">
-        <v>126.37845105399929</v>
+        <v>126.21894563199891</v>
       </c>
       <c r="M3">
-        <v>1.1879899905508486</v>
+        <v>1.1718156940141815</v>
       </c>
       <c r="N3">
         <v>1.2502251600686518</v>
       </c>
       <c r="O3">
-        <v>1.4185041038211952</v>
+        <v>1.4172255417747834</v>
       </c>
       <c r="P3">
-        <v>1.1879899905508486</v>
+        <v>1.1718156940141815</v>
       </c>
       <c r="Q3">
         <v>1.2502251600686518</v>
       </c>
       <c r="R3">
-        <v>1.4185041038211952</v>
+        <v>1.4172255417747834</v>
       </c>
       <c r="S3">
         <v>83.441196534470748</v>
@@ -1243,46 +1243,46 @@
         <v>71.142607476102043</v>
       </c>
       <c r="V3">
-        <v>5.1091309723327304E-15</v>
+        <v>55.969034484618319</v>
       </c>
       <c r="W3">
         <v>180.19837984810317</v>
       </c>
       <c r="X3">
-        <v>47.901699647906668</v>
+        <v>50.195285369280967</v>
       </c>
       <c r="Y3">
-        <v>28.046871074079426</v>
+        <v>28.046871074079434</v>
       </c>
       <c r="Z3">
-        <v>15.907903970049285</v>
+        <v>15.907903970049288</v>
       </c>
       <c r="AA3">
-        <v>4.6914221870849087</v>
+        <v>3.975259978741601</v>
       </c>
       <c r="AB3">
-        <v>1.7202873091103372</v>
+        <v>1.7202873091103368</v>
       </c>
       <c r="AC3">
-        <v>1.3724134227036469</v>
+        <v>1.1650668813300726</v>
       </c>
       <c r="AD3">
-        <v>0.88425746063925748</v>
+        <v>0.88359403954016036</v>
       </c>
       <c r="AE3">
-        <v>1224.9234122189714</v>
+        <v>1069.9580049106642</v>
       </c>
       <c r="AF3">
-        <v>14.347559276187184</v>
+        <v>9.323529947849563</v>
       </c>
       <c r="AG3">
-        <v>62031.105484962434</v>
+        <v>62021.423304265176</v>
       </c>
       <c r="AH3">
-        <v>2566.6707829161892</v>
+        <v>1925.002745086342</v>
       </c>
       <c r="AI3">
-        <v>2566.6707829161892</v>
+        <v>1925.002745086342</v>
       </c>
       <c r="AJ3">
         <v>21.73557266005486</v>
@@ -1297,136 +1297,136 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-6.42185145245124</v>
+        <v>-6.3908220273567551</v>
       </c>
       <c r="AO3">
-        <v>-3.6058273455266119</v>
+        <v>-3.6058080683176734</v>
       </c>
       <c r="AP3">
-        <v>-4.5389154796042925</v>
+        <v>-3.8461114627771096</v>
       </c>
       <c r="AQ3">
-        <v>-1.6648383135739739</v>
+        <v>-1.6648800649135422</v>
       </c>
       <c r="AR3">
-        <v>1840.1007622388279</v>
+        <v>1840.1500148508144</v>
       </c>
       <c r="AS3">
-        <v>133.09723012310982</v>
+        <v>99.7487949437495</v>
       </c>
       <c r="AT3">
-        <v>-0.30411265002603738</v>
+        <v>-0.36349288131767327</v>
       </c>
       <c r="AU3">
-        <v>-0.39905931215246609</v>
+        <v>-0.39566855006539486</v>
       </c>
       <c r="AV3">
-        <v>-0.685685911796377</v>
+        <v>-0.45266913571852652</v>
       </c>
       <c r="AW3">
-        <v>0.24566091163902223</v>
+        <v>0.24108475699374146</v>
       </c>
       <c r="AX3">
-        <v>5.4877037134012756</v>
+        <v>3.6391266471254151</v>
       </c>
       <c r="AY3">
-        <v>6.4362343984614E-05</v>
+        <v>6.3189296965147793E-05</v>
       </c>
       <c r="AZ3">
-        <v>-5.4807156895017686</v>
+        <v>-5.7661880296319534</v>
       </c>
       <c r="BA3">
-        <v>0.00010445174248096017</v>
+        <v>0.00010358228224352701</v>
       </c>
       <c r="BB3">
-        <v>-0.0040658457937721333</v>
+        <v>-0.0043521380600878724</v>
       </c>
       <c r="BC3">
-        <v>-0.00551601749156846</v>
+        <v>-0.0036547162620744786</v>
       </c>
       <c r="BD3">
-        <v>-0.46132590596181439</v>
+        <v>-0.26941544141375362</v>
       </c>
       <c r="BE3">
-        <v>0.0011225313339198852</v>
+        <v>0.0011067579103945806</v>
       </c>
       <c r="BF3">
-        <v>-250706871834.84714</v>
+        <v>-146409498812.29971</v>
       </c>
       <c r="BG3">
-        <v>8433919570.539423</v>
+        <v>11095451438.974327</v>
       </c>
       <c r="BH3">
-        <v>39.52930053058067</v>
+        <v>37.203949274529911</v>
       </c>
       <c r="BI3">
-        <v>48.868488001665114</v>
+        <v>48.822064722659661</v>
       </c>
       <c r="BJ3">
-        <v>0.74433534780708666</v>
+        <v>-0.58802716499338814</v>
       </c>
       <c r="BK3">
-        <v>0.00012101011344287758</v>
+        <v>0.00011956693394155613</v>
       </c>
       <c r="BL3">
-        <v>-7.7200454276664665</v>
+        <v>-6.7931135129717166</v>
       </c>
       <c r="BM3">
-        <v>2.0229440799105081E-05</v>
+        <v>2.0637944508668541E-05</v>
       </c>
       <c r="BN3">
-        <v>-11.574664910077269</v>
+        <v>11.271089382057392</v>
       </c>
       <c r="BO3">
-        <v>0.0535417517909664</v>
+        <v>0.047899049545424011</v>
       </c>
       <c r="BP3">
-        <v>11.510466063377438</v>
+        <v>-12.869447068042165</v>
       </c>
       <c r="BQ3">
-        <v>5.5934016334737029</v>
+        <v>5.553749901515193</v>
       </c>
       <c r="BR3">
-        <v>-26.080393799936541</v>
+        <v>32.399645072271483</v>
       </c>
       <c r="BS3">
-        <v>-9.92430721675723</v>
+        <v>-11.215735238303571</v>
       </c>
       <c r="BT3">
-        <v>-0.037569175318620668</v>
+        <v>0.31173364721385194</v>
       </c>
       <c r="BU3">
-        <v>1.209663105956462</v>
+        <v>1.0346890393841091</v>
       </c>
       <c r="BV3">
-        <v>19.284778073899567</v>
+        <v>19.285002065832682</v>
       </c>
       <c r="BW3">
-        <v>-2.0361931118022873</v>
+        <v>-2.0340705663613368</v>
       </c>
       <c r="BX3">
-        <v>4.831407481611361</v>
+        <v>-4.4617992700998039</v>
       </c>
       <c r="BY3">
-        <v>0.010202830686530197</v>
+        <v>0.013265730532611047</v>
       </c>
       <c r="BZ3">
-        <v>-9.2764118122578836</v>
+        <v>9.712624599118115</v>
       </c>
       <c r="CA3">
-        <v>-0.017325644535801144</v>
+        <v>-0.026292108603101442</v>
       </c>
       <c r="CB3">
-        <v>51.981767025742265</v>
+        <v>56.862568050573117</v>
       </c>
       <c r="CC3">
-        <v>0.013237399795289486</v>
+        <v>0.017294179633578644</v>
       </c>
       <c r="CD3">
-        <v>4.0398780575505322</v>
+        <v>3.6931149471340734</v>
       </c>
       <c r="CE3">
-        <v>15864.142750657744</v>
+        <v>12142.813619922206</v>
       </c>
     </row>
     <row r="4" spans="1:83">
@@ -1449,7 +1449,7 @@
         <v>321.98096759425704</v>
       </c>
       <c r="G4">
-        <v>58.662706136568943</v>
+        <v>43.997029602426714</v>
       </c>
       <c r="H4">
         <v>15427542.710989449</v>
@@ -1458,31 +1458,31 @@
         <v>47914455398588.664</v>
       </c>
       <c r="J4">
-        <v>126.37845105399929</v>
+        <v>126.21894563199891</v>
       </c>
       <c r="K4">
         <v>139.19764769616907</v>
       </c>
       <c r="L4">
-        <v>166.48888186767266</v>
+        <v>164.34965460071388</v>
       </c>
       <c r="M4">
-        <v>1.4185041038211952</v>
+        <v>1.4172255417747834</v>
       </c>
       <c r="N4">
         <v>1.5050869773596172</v>
       </c>
       <c r="O4">
-        <v>1.7105297219569222</v>
+        <v>1.6947929446409555</v>
       </c>
       <c r="P4">
-        <v>1.4185041038211952</v>
+        <v>1.4172255417747834</v>
       </c>
       <c r="Q4">
         <v>1.5050869773596172</v>
       </c>
       <c r="R4">
-        <v>1.7105297219569222</v>
+        <v>1.6947929446409555</v>
       </c>
       <c r="S4">
         <v>71.142607476102043</v>
@@ -1494,46 +1494,46 @@
         <v>61.0312751794986</v>
       </c>
       <c r="V4">
-        <v>47.901699647906668</v>
+        <v>50.195285369280967</v>
       </c>
       <c r="W4">
         <v>185.95319719491755</v>
       </c>
       <c r="X4">
-        <v>35.143874297832284</v>
+        <v>61.220150588891464</v>
       </c>
       <c r="Y4">
         <v>29.965724288101779</v>
       </c>
       <c r="Z4">
-        <v>20.223705374486514</v>
+        <v>20.223705374486517</v>
       </c>
       <c r="AA4">
-        <v>5.4735761092633268</v>
+        <v>5.4395443500332874</v>
       </c>
       <c r="AB4">
-        <v>2.7190109042326691</v>
+        <v>2.7190109042326682</v>
       </c>
       <c r="AC4">
-        <v>1.4967606309540253</v>
+        <v>1.4876025211446644</v>
       </c>
       <c r="AD4">
-        <v>1.0977399589442225</v>
+        <v>1.0969148292950859</v>
       </c>
       <c r="AE4">
-        <v>1731.708560064613</v>
+        <v>1721.3612374398929</v>
       </c>
       <c r="AF4">
-        <v>51.368203371388191</v>
+        <v>34.772672879816739</v>
       </c>
       <c r="AG4">
-        <v>80838.220536479</v>
+        <v>80837.568764425741</v>
       </c>
       <c r="AH4">
-        <v>6705.2748121477571</v>
+        <v>5028.954732004755</v>
       </c>
       <c r="AI4">
-        <v>6705.2748121477571</v>
+        <v>5028.954732004755</v>
       </c>
       <c r="AJ4">
         <v>23.222632423234934</v>
@@ -1548,136 +1548,136 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-6.8837633061142327</v>
+        <v>-6.88203329127896</v>
       </c>
       <c r="AO4">
-        <v>-4.6021318514471563</v>
+        <v>-4.6020939566387966</v>
       </c>
       <c r="AP4">
-        <v>-5.295576084556517</v>
+        <v>-5.2626560225555838</v>
       </c>
       <c r="AQ4">
-        <v>-2.6313261725324262</v>
+        <v>-2.6313924486148541</v>
       </c>
       <c r="AR4">
-        <v>2244.1101067653412</v>
+        <v>2244.1190090163541</v>
       </c>
       <c r="AS4">
-        <v>273.48316409667376</v>
+        <v>204.96039077838822</v>
       </c>
       <c r="AT4">
-        <v>-0.49071222428765549</v>
+        <v>-0.500837778906274</v>
       </c>
       <c r="AU4">
-        <v>-0.70074601202952824</v>
+        <v>-0.6493196118125274</v>
       </c>
       <c r="AV4">
-        <v>-0.55574455070632756</v>
+        <v>-0.54016166494997375</v>
       </c>
       <c r="AW4">
-        <v>0.39182398147311748</v>
+        <v>0.32864819532357004</v>
       </c>
       <c r="AX4">
-        <v>4.4298150762024688</v>
+        <v>4.69495471806936</v>
       </c>
       <c r="AY4">
-        <v>0.0066089063721072308</v>
+        <v>0.0055301071012812805</v>
       </c>
       <c r="AZ4">
-        <v>-9.11766696685729</v>
+        <v>-8.9583577022461416</v>
       </c>
       <c r="BA4">
-        <v>0.011917444110532416</v>
+        <v>0.011032791839681245</v>
       </c>
       <c r="BB4">
-        <v>0.046699963677636319</v>
+        <v>0.046105970407924385</v>
       </c>
       <c r="BC4">
-        <v>0.030594510871667865</v>
+        <v>0.031845830288482257</v>
       </c>
       <c r="BD4">
-        <v>-0.26149318023063456</v>
+        <v>-0.27808841662953548</v>
       </c>
       <c r="BE4">
-        <v>-0.021123585808660084</v>
+        <v>-0.018635645919025175</v>
       </c>
       <c r="BF4">
-        <v>-116524220198.60277</v>
+        <v>-123918747406.99587</v>
       </c>
       <c r="BG4">
-        <v>-77239072022.704453</v>
+        <v>-90923157631.8315</v>
       </c>
       <c r="BH4">
-        <v>35.654012461538763</v>
+        <v>35.547760657513216</v>
       </c>
       <c r="BI4">
-        <v>47.588086992158338</v>
+        <v>46.874327538081054</v>
       </c>
       <c r="BJ4">
-        <v>-1.7151362810003259</v>
+        <v>-1.3882608938435999</v>
       </c>
       <c r="BK4">
-        <v>0.0132562451977442</v>
+        <v>0.011832735883000422</v>
       </c>
       <c r="BL4">
-        <v>-9.9906666477001238</v>
+        <v>-10.018358359369017</v>
       </c>
       <c r="BM4">
-        <v>0.0031583351342482939</v>
+        <v>0.0035058439572423815</v>
       </c>
       <c r="BN4">
-        <v>7.1127493274051643</v>
+        <v>8.7362065671163673</v>
       </c>
       <c r="BO4">
-        <v>0.10457734880443771</v>
+        <v>0.11737883228328468</v>
       </c>
       <c r="BP4">
-        <v>-7.5164679709393658</v>
+        <v>-8.6323477105084212</v>
       </c>
       <c r="BQ4">
-        <v>4.96046220740237</v>
+        <v>5.1894656445569938</v>
       </c>
       <c r="BR4">
-        <v>32.904098906861662</v>
+        <v>32.610381240604916</v>
       </c>
       <c r="BS4">
-        <v>-10.163326662858767</v>
+        <v>-11.054891121615118</v>
       </c>
       <c r="BT4">
-        <v>-0.029470642252624357</v>
+        <v>0.3194143795272536</v>
       </c>
       <c r="BU4">
-        <v>1.3295849253459411</v>
+        <v>1.1547389607175078</v>
       </c>
       <c r="BV4">
-        <v>19.26639120443831</v>
+        <v>19.26585910516344</v>
       </c>
       <c r="BW4">
-        <v>-2.5435894636700391</v>
+        <v>-2.5476166003035283</v>
       </c>
       <c r="BX4">
-        <v>-5.8419393556156125</v>
+        <v>-5.255076733415736</v>
       </c>
       <c r="BY4">
-        <v>0.34313088027250116</v>
+        <v>0.39272155512554008</v>
       </c>
       <c r="BZ4">
-        <v>14.132629699949517</v>
+        <v>12.9571293430661</v>
       </c>
       <c r="CA4">
-        <v>-0.66548185152370964</v>
+        <v>-0.88035512078204026</v>
       </c>
       <c r="CB4">
-        <v>62.0471945144914</v>
+        <v>60.871710874727484</v>
       </c>
       <c r="CC4">
-        <v>0.35171675428320165</v>
+        <v>0.4031094646047963</v>
       </c>
       <c r="CD4">
-        <v>3.384520470961077</v>
+        <v>3.4498783914941202</v>
       </c>
       <c r="CE4">
-        <v>597.07135768376963</v>
+        <v>520.95030863609588</v>
       </c>
     </row>
     <row r="5" spans="1:83">
@@ -1700,7 +1700,7 @@
         <v>410.0602845013932</v>
       </c>
       <c r="G5">
-        <v>120.92057816393815</v>
+        <v>90.69043362295362</v>
       </c>
       <c r="H5">
         <v>19759732.473881818</v>
@@ -1709,7 +1709,7 @@
         <v>48187384198663.312</v>
       </c>
       <c r="J5">
-        <v>166.48888186767266</v>
+        <v>164.34965460071388</v>
       </c>
       <c r="K5">
         <v>173.68488655089271</v>
@@ -1718,7 +1718,7 @@
         <v>197.57806825354194</v>
       </c>
       <c r="M5">
-        <v>1.7105297219569222</v>
+        <v>1.6947929446409555</v>
       </c>
       <c r="N5">
         <v>1.7483993190861489</v>
@@ -1727,7 +1727,7 @@
         <v>1.9172557051837726</v>
       </c>
       <c r="P5">
-        <v>1.7105297219569222</v>
+        <v>1.6947929446409555</v>
       </c>
       <c r="Q5">
         <v>1.7483993190861489</v>
@@ -1745,7 +1745,7 @@
         <v>56.148773165138714</v>
       </c>
       <c r="V5">
-        <v>35.143874297832284</v>
+        <v>61.220150588891464</v>
       </c>
       <c r="W5">
         <v>167.08188774140984</v>
@@ -1754,37 +1754,37 @@
         <v>45.965955812883692</v>
       </c>
       <c r="Y5">
-        <v>33.816879739610627</v>
+        <v>33.81687973961062</v>
       </c>
       <c r="Z5">
-        <v>29.0355321883068</v>
+        <v>29.035532188306803</v>
       </c>
       <c r="AA5">
-        <v>6.4431897040053192</v>
+        <v>5.9942399377313027</v>
       </c>
       <c r="AB5">
-        <v>3.386992074068695</v>
+        <v>3.3869920740686945</v>
       </c>
       <c r="AC5">
-        <v>1.5601462650526363</v>
+        <v>1.4531462890140428</v>
       </c>
       <c r="AD5">
-        <v>0.95341937133245336</v>
+        <v>0.95270365782363642</v>
       </c>
       <c r="AE5">
-        <v>2927.417433775172</v>
+        <v>2729.636440802064</v>
       </c>
       <c r="AF5">
-        <v>177.02703078190297</v>
+        <v>116.82068594496569</v>
       </c>
       <c r="AG5">
-        <v>131122.30013556063</v>
+        <v>131109.83440764336</v>
       </c>
       <c r="AH5">
-        <v>28487.486547342607</v>
+        <v>21365.610496570262</v>
       </c>
       <c r="AI5">
-        <v>28487.486547342607</v>
+        <v>21365.610496570262</v>
       </c>
       <c r="AJ5">
         <v>26.207174581978549</v>
@@ -1799,136 +1799,136 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>-7.7823085738577173</v>
+        <v>-7.7592685913428125</v>
       </c>
       <c r="AO5">
-        <v>-6.58922709586921</v>
+        <v>-6.589186150476718</v>
       </c>
       <c r="AP5">
-        <v>-6.2336168802030985</v>
+        <v>-5.7993340949272794</v>
       </c>
       <c r="AQ5">
-        <v>-3.2778041724521665</v>
+        <v>-3.2778864819037996</v>
       </c>
       <c r="AR5">
-        <v>3225.2008587498917</v>
+        <v>3225.3592428517177</v>
       </c>
       <c r="AS5">
-        <v>809.33128774935858</v>
+        <v>606.54801085480688</v>
       </c>
       <c r="AT5">
-        <v>-0.30098665116719331</v>
+        <v>-0.40969314443851923</v>
       </c>
       <c r="AU5">
         <v>-0.87532795587262069</v>
       </c>
       <c r="AV5">
-        <v>-0.59726755146903954</v>
+        <v>-0.45736026321305129</v>
       </c>
       <c r="AW5">
         <v>0.46601543748101987</v>
       </c>
       <c r="AX5">
-        <v>5.6475009061691575</v>
+        <v>4.6649795243845409</v>
       </c>
       <c r="AY5">
         <v>0.033656751636888568</v>
       </c>
       <c r="AZ5">
-        <v>-9.4084834302834839</v>
+        <v>-10.094431392523985</v>
       </c>
       <c r="BA5">
         <v>0.0645421882304757</v>
       </c>
       <c r="BB5">
-        <v>0.071782020803440844</v>
+        <v>0.078750721878436541</v>
       </c>
       <c r="BC5">
-        <v>0.060156795177012945</v>
+        <v>0.048952770695087813</v>
       </c>
       <c r="BD5">
-        <v>-0.45671406945880172</v>
+        <v>-0.30855572028601924</v>
       </c>
       <c r="BE5">
-        <v>-0.070881952154191089</v>
+        <v>-0.070882561175678774</v>
       </c>
       <c r="BF5">
-        <v>-141607946128.30005</v>
+        <v>-95665535853.056839</v>
       </c>
       <c r="BG5">
-        <v>-87580887118.925385</v>
+        <v>-116862243230.81058</v>
       </c>
       <c r="BH5">
-        <v>37.359231266179044</v>
+        <v>36.118134674019217</v>
       </c>
       <c r="BI5">
         <v>50.49640689290311</v>
       </c>
       <c r="BJ5">
-        <v>-1.2202689188722298</v>
+        <v>-2.1817973043186791</v>
       </c>
       <c r="BK5">
         <v>0.07120971973591235</v>
       </c>
       <c r="BL5">
-        <v>-10.90526344059302</v>
+        <v>-10.904097377782742</v>
       </c>
       <c r="BM5">
         <v>0.015087968963984896</v>
       </c>
       <c r="BN5">
-        <v>11.283543331485054</v>
+        <v>5.9402878965355947</v>
       </c>
       <c r="BO5">
-        <v>0.075439593405172978</v>
+        <v>0.066377117519424711</v>
       </c>
       <c r="BP5">
-        <v>-10.283447378300402</v>
+        <v>-6.3692537036919541</v>
       </c>
       <c r="BQ5">
-        <v>5.6379552191049713</v>
+        <v>4.7871170974187223</v>
       </c>
       <c r="BR5">
-        <v>32.014830992900876</v>
+        <v>33.131892141337133</v>
       </c>
       <c r="BS5">
-        <v>-12.780220350598773</v>
+        <v>-9.3123726297071681</v>
       </c>
       <c r="BT5">
-        <v>-0.034946768773827956</v>
+        <v>0.3140189032438736</v>
       </c>
       <c r="BU5">
-        <v>1.2486908864961408</v>
+        <v>1.0737823966370845</v>
       </c>
       <c r="BV5">
-        <v>19.279086941029206</v>
+        <v>19.279462488863874</v>
       </c>
       <c r="BW5">
-        <v>-2.2021860352390448</v>
+        <v>-2.1988958033648616</v>
       </c>
       <c r="BX5">
-        <v>-3.2053937493109439</v>
+        <v>-4.3560566518064956</v>
       </c>
       <c r="BY5">
-        <v>0.50230862637285612</v>
+        <v>0.654317661814743</v>
       </c>
       <c r="BZ5">
-        <v>7.9899555123618766</v>
+        <v>10.198877431095518</v>
       </c>
       <c r="CA5">
-        <v>-0.896047632878628</v>
+        <v>-1.3539831554556987</v>
       </c>
       <c r="CB5">
-        <v>56.17751818849186</v>
+        <v>58.386340003406595</v>
       </c>
       <c r="CC5">
-        <v>0.50988662261048145</v>
+        <v>0.6646716380707467</v>
       </c>
       <c r="CD5">
-        <v>3.7381501848370933</v>
+        <v>3.5967317010750697</v>
       </c>
       <c r="CE5">
-        <v>411.85626507488439</v>
+        <v>315.94548040223117</v>
       </c>
     </row>
   </sheetData>
@@ -2795,7 +2795,7 @@
         <v>151.95799581723239</v>
       </c>
       <c r="G3">
-        <v>66.722097061129247</v>
+        <v>55.601747550941042</v>
       </c>
       <c r="H3">
         <v>5388027.5545115508</v>
@@ -2804,31 +2804,31 @@
         <v>35457348101589.906</v>
       </c>
       <c r="J3">
-        <v>97.126137383957371</v>
+        <v>95.793399708605349</v>
       </c>
       <c r="K3">
         <v>111.61678704621447</v>
       </c>
       <c r="L3">
-        <v>126.37845105399929</v>
+        <v>126.70749296979982</v>
       </c>
       <c r="M3">
-        <v>1.1879899905508486</v>
+        <v>1.17633455788332</v>
       </c>
       <c r="N3">
         <v>1.2981170396729074</v>
       </c>
       <c r="O3">
-        <v>1.4185041038211952</v>
+        <v>1.4211401780530102</v>
       </c>
       <c r="P3">
-        <v>1.1879899905508486</v>
+        <v>1.17633455788332</v>
       </c>
       <c r="Q3">
         <v>1.2981170396729074</v>
       </c>
       <c r="R3">
-        <v>1.4185041038211952</v>
+        <v>1.4211401780530102</v>
       </c>
       <c r="S3">
         <v>83.441196534470748</v>
@@ -2840,46 +2840,46 @@
         <v>71.142607476102043</v>
       </c>
       <c r="V3">
-        <v>5.1091309723327304E-15</v>
+        <v>47.484278169761218</v>
       </c>
       <c r="W3">
         <v>153.25040447078592</v>
       </c>
       <c r="X3">
-        <v>47.901699647906668</v>
+        <v>42.791066555318523</v>
       </c>
       <c r="Y3">
         <v>32.549285640722566</v>
       </c>
       <c r="Z3">
-        <v>17.61038689278082</v>
+        <v>17.610386892780824</v>
       </c>
       <c r="AA3">
-        <v>2.2885443687170737</v>
+        <v>1.8158099718494121</v>
       </c>
       <c r="AB3">
         <v>1.9623978389259515</v>
       </c>
       <c r="AC3">
-        <v>0.57580470692334951</v>
+        <v>0.45705133723237767</v>
       </c>
       <c r="AD3">
-        <v>0.91299746401564541</v>
+        <v>0.91191898326761067</v>
       </c>
       <c r="AE3">
-        <v>151.25052759677877</v>
+        <v>123.77060458459179</v>
       </c>
       <c r="AF3">
-        <v>46.022095240219677</v>
+        <v>32.69900240387053</v>
       </c>
       <c r="AG3">
-        <v>44980.576587945383</v>
+        <v>44978.90336877056</v>
       </c>
       <c r="AH3">
-        <v>5782.1813309565441</v>
+        <v>4818.4830085822014</v>
       </c>
       <c r="AI3">
-        <v>5782.1813309565441</v>
+        <v>4818.4830085822014</v>
       </c>
       <c r="AJ3">
         <v>25.224823161491528</v>
@@ -2894,136 +2894,136 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-7.3470913805083544</v>
+        <v>-7.3387140950312606</v>
       </c>
       <c r="AO3">
-        <v>-3.993575503126833</v>
+        <v>-3.9935397573770697</v>
       </c>
       <c r="AP3">
-        <v>-2.2148214789706424</v>
+        <v>-1.75732521034682</v>
       </c>
       <c r="AQ3">
-        <v>-1.8990047487546939</v>
+        <v>-1.8990799196496033</v>
       </c>
       <c r="AR3">
-        <v>1140.0426033675517</v>
+        <v>1140.0121016932674</v>
       </c>
       <c r="AS3">
-        <v>271.4257429436729</v>
+        <v>225.92479795203732</v>
       </c>
       <c r="AT3">
-        <v>-0.61596495895875791</v>
+        <v>-0.65551363969130583</v>
       </c>
       <c r="AU3">
-        <v>-0.33549067399876747</v>
+        <v>-0.34307407496404979</v>
       </c>
       <c r="AV3">
-        <v>-0.68568591179637717</v>
+        <v>-0.45446285180522289</v>
       </c>
       <c r="AW3">
-        <v>0.23883126678148417</v>
+        <v>0.25028253753409563</v>
       </c>
       <c r="AX3">
-        <v>1.1857174093350535</v>
+        <v>0.78703345723945461</v>
       </c>
       <c r="AY3">
-        <v>0.54761090797638157</v>
+        <v>0.54892971070988306</v>
       </c>
       <c r="AZ3">
-        <v>-1.3551324382320296</v>
+        <v>-1.406689227530916</v>
       </c>
       <c r="BA3">
-        <v>0.84791068286559179</v>
+        <v>0.84853010711925714</v>
       </c>
       <c r="BB3">
-        <v>-0.4731858079233881</v>
+        <v>-0.4991560210133128</v>
       </c>
       <c r="BC3">
-        <v>-0.58489508285376912</v>
+        <v>-0.38782467256115116</v>
       </c>
       <c r="BD3">
-        <v>-0.23958897655502151</v>
+        <v>-0.14852615321077181</v>
       </c>
       <c r="BE3">
-        <v>-0.10571530338961899</v>
+        <v>-0.10684560883685462</v>
       </c>
       <c r="BF3">
-        <v>-210157915017.65274</v>
+        <v>-130284716267.62993</v>
       </c>
       <c r="BG3">
-        <v>-389481492223.66626</v>
+        <v>-472925547816.74469</v>
       </c>
       <c r="BH3">
-        <v>58.18098937721863</v>
+        <v>56.941950011015052</v>
       </c>
       <c r="BI3">
-        <v>44.747063750788371</v>
+        <v>44.864143087796691</v>
       </c>
       <c r="BJ3">
-        <v>-0.52632516878253266</v>
+        <v>-0.74965435209430065</v>
       </c>
       <c r="BK3">
-        <v>0.98583576025527131</v>
+        <v>0.98764820925426289</v>
       </c>
       <c r="BL3">
-        <v>-1.722002182534899</v>
+        <v>-1.4269599146618968</v>
       </c>
       <c r="BM3">
-        <v>0.21669814594089704</v>
+        <v>0.21419193435958744</v>
       </c>
       <c r="BN3">
-        <v>0.63031341634109661</v>
+        <v>0.30010830715342096</v>
       </c>
       <c r="BO3">
-        <v>0.10024148615780289</v>
+        <v>0.084323247218255112</v>
       </c>
       <c r="BP3">
-        <v>-1.5143963106485963</v>
+        <v>-0.8119916601090873</v>
       </c>
       <c r="BQ3">
-        <v>2.1249205553310415</v>
+        <v>1.9795325496000655</v>
       </c>
       <c r="BR3">
-        <v>39.46470934644011</v>
+        <v>39.494191709441736</v>
       </c>
       <c r="BS3">
-        <v>-3.1199352983421047</v>
+        <v>-2.3379118479920815</v>
       </c>
       <c r="BT3">
-        <v>-0.032664984598752653</v>
+        <v>-0.036557724007809586</v>
       </c>
       <c r="BU3">
-        <v>1.7441060387452956</v>
+        <v>1.5499928258460409</v>
       </c>
       <c r="BV3">
-        <v>21.344645980888984</v>
+        <v>21.345339262131507</v>
       </c>
       <c r="BW3">
-        <v>-2.3402104033904432</v>
+        <v>-2.3338784385919018</v>
       </c>
       <c r="BX3">
-        <v>-7.4523248804927249</v>
+        <v>-12.015402122123518</v>
       </c>
       <c r="BY3">
-        <v>37.361585410491706</v>
+        <v>46.817965821888144</v>
       </c>
       <c r="BZ3">
-        <v>12.36766167313929</v>
+        <v>15.413231874595889</v>
       </c>
       <c r="CA3">
-        <v>-50.9293977942037</v>
+        <v>-71.441848814340048</v>
       </c>
       <c r="CB3">
-        <v>47.825471522005792</v>
+        <v>50.870746812100251</v>
       </c>
       <c r="CC3">
-        <v>37.363615459672147</v>
+        <v>46.820354358689606</v>
       </c>
       <c r="CD3">
-        <v>4.3909655946282369</v>
+        <v>4.1281092407719253</v>
       </c>
       <c r="CE3">
-        <v>5.6204411006922053</v>
+        <v>4.4852287616448834</v>
       </c>
     </row>
     <row r="4" spans="1:83">
@@ -3046,7 +3046,7 @@
         <v>173.53724208300113</v>
       </c>
       <c r="G4">
-        <v>107.86906381219706</v>
+        <v>89.890886510164236</v>
       </c>
       <c r="H4">
         <v>6598347.0808880907</v>
@@ -3055,31 +3055,31 @@
         <v>38022657279134.164</v>
       </c>
       <c r="J4">
-        <v>126.37845105399929</v>
+        <v>126.70749296979982</v>
       </c>
       <c r="K4">
         <v>146.7059356352807</v>
       </c>
       <c r="L4">
-        <v>166.48888186767266</v>
+        <v>165.28254301559932</v>
       </c>
       <c r="M4">
-        <v>1.4185041038211952</v>
+        <v>1.4211401780530102</v>
       </c>
       <c r="N4">
         <v>1.5626714059803666</v>
       </c>
       <c r="O4">
-        <v>1.7105297219569222</v>
+        <v>1.7016626849660006</v>
       </c>
       <c r="P4">
-        <v>1.4185041038211952</v>
+        <v>1.4211401780530102</v>
       </c>
       <c r="Q4">
         <v>1.5626714059803666</v>
       </c>
       <c r="R4">
-        <v>1.7105297219569222</v>
+        <v>1.7016626849660006</v>
       </c>
       <c r="S4">
         <v>71.142607476102043</v>
@@ -3091,46 +3091,46 @@
         <v>61.0312751794986</v>
       </c>
       <c r="V4">
-        <v>47.901699647906668</v>
+        <v>42.791066555318523</v>
       </c>
       <c r="W4">
         <v>157.44194728826497</v>
       </c>
       <c r="X4">
-        <v>35.143874297832284</v>
+        <v>51.470815454060336</v>
       </c>
       <c r="Y4">
         <v>34.783720175771847</v>
       </c>
       <c r="Z4">
-        <v>22.391464965209217</v>
+        <v>22.391464965209206</v>
       </c>
       <c r="AA4">
-        <v>2.2599823541710657</v>
+        <v>2.316610858340741</v>
       </c>
       <c r="AB4">
-        <v>3.11928460825156</v>
+        <v>3.1192846082515611</v>
       </c>
       <c r="AC4">
-        <v>0.53217801490345151</v>
+        <v>0.54548655209826513</v>
       </c>
       <c r="AD4">
-        <v>1.1395185482673504</v>
+        <v>1.1381697319935322</v>
       </c>
       <c r="AE4">
-        <v>183.14677724868704</v>
+        <v>187.33543602876398</v>
       </c>
       <c r="AF4">
-        <v>154.48705715278854</v>
+        <v>113.96677237551232</v>
       </c>
       <c r="AG4">
-        <v>58662.007646329868</v>
+        <v>58662.262761005935</v>
       </c>
       <c r="AH4">
-        <v>15114.952532532776</v>
+        <v>12595.787939302041</v>
       </c>
       <c r="AI4">
-        <v>15114.952532532776</v>
+        <v>12595.787939302041</v>
       </c>
       <c r="AJ4">
         <v>26.956449982266708</v>
@@ -3145,136 +3145,136 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-7.8479235584319911</v>
+        <v>-7.8489705066256041</v>
       </c>
       <c r="AO4">
-        <v>-5.0997171729092434</v>
+        <v>-5.0996461129917678</v>
       </c>
       <c r="AP4">
-        <v>-2.1871842044753995</v>
+        <v>-2.2419871848959296</v>
       </c>
       <c r="AQ4">
-        <v>-3.018463283233292</v>
+        <v>-3.0185833362921755</v>
       </c>
       <c r="AR4">
-        <v>1391.2985486567111</v>
+        <v>1391.3028349038536</v>
       </c>
       <c r="AS4">
-        <v>557.96561721981664</v>
+        <v>464.43132970014068</v>
       </c>
       <c r="AT4">
-        <v>-0.93332670120927219</v>
+        <v>-0.92097441961324589</v>
       </c>
       <c r="AU4">
-        <v>-0.59515630225117089</v>
+        <v>-0.561316149882912</v>
       </c>
       <c r="AV4">
-        <v>-0.52082402136143036</v>
+        <v>-0.54081697814217622</v>
       </c>
       <c r="AW4">
-        <v>0.38964732755710918</v>
+        <v>0.34164053914809683</v>
       </c>
       <c r="AX4">
-        <v>1.0172269204918283</v>
+        <v>1.1042541358513986</v>
       </c>
       <c r="AY4">
-        <v>1.0639626706367995</v>
+        <v>0.90336393189173114</v>
       </c>
       <c r="AZ4">
-        <v>-2.4284392731755342</v>
+        <v>-2.3764142699615247</v>
       </c>
       <c r="BA4">
-        <v>1.8242544014422235</v>
+        <v>1.6981941208715485</v>
       </c>
       <c r="BB4">
-        <v>-0.59499069724666587</v>
+        <v>-0.58496390467188453</v>
       </c>
       <c r="BC4">
-        <v>-0.35452677199906346</v>
+        <v>-0.37492598600121019</v>
       </c>
       <c r="BD4">
-        <v>-0.15847657700215528</v>
+        <v>-0.17513866508680365</v>
       </c>
       <c r="BE4">
-        <v>-0.27441002278081472</v>
+        <v>-0.24547677963278181</v>
       </c>
       <c r="BF4">
-        <v>-113905514495.90981</v>
+        <v>-125881052415.81474</v>
       </c>
       <c r="BG4">
-        <v>-491804538330.01672</v>
+        <v>-528553445761.88141</v>
       </c>
       <c r="BH4">
-        <v>58.292219996306677</v>
+        <v>58.432399762615667</v>
       </c>
       <c r="BI4">
-        <v>43.432808476605274</v>
+        <v>42.908711359301535</v>
       </c>
       <c r="BJ4">
-        <v>-1.5313283954894339</v>
+        <v>-1.4466781979066787</v>
       </c>
       <c r="BK4">
-        <v>2.0268107861274949</v>
+        <v>1.8178446336241918</v>
       </c>
       <c r="BL4">
-        <v>-2.1417519129073659</v>
+        <v>-2.1849128519744605</v>
       </c>
       <c r="BM4">
-        <v>0.59326109170175823</v>
+        <v>0.62878498201635513</v>
       </c>
       <c r="BN4">
-        <v>0.25018603173063841</v>
+        <v>0.27633924857497466</v>
       </c>
       <c r="BO4">
-        <v>0.17141124494978147</v>
+        <v>0.179316197567186</v>
       </c>
       <c r="BP4">
-        <v>-0.80993895141366834</v>
+        <v>-0.80829591313355054</v>
       </c>
       <c r="BQ4">
-        <v>2.0664348154935817</v>
+        <v>2.0823021613170036</v>
       </c>
       <c r="BR4">
-        <v>39.489076832088919</v>
+        <v>39.486479331488219</v>
       </c>
       <c r="BS4">
-        <v>-2.6542530054698861</v>
+        <v>-2.7344353379773687</v>
       </c>
       <c r="BT4">
-        <v>-0.020397235699248607</v>
+        <v>-0.024645205781627912</v>
       </c>
       <c r="BU4">
-        <v>1.8843290237089536</v>
+        <v>1.6902498748062658</v>
       </c>
       <c r="BV4">
-        <v>21.320969254370617</v>
+        <v>21.320632495928741</v>
       </c>
       <c r="BW4">
-        <v>-2.9417997185605382</v>
+        <v>-2.9442393760507133</v>
       </c>
       <c r="BX4">
-        <v>-17.30746329719258</v>
+        <v>-16.110464881553479</v>
       </c>
       <c r="BY4">
-        <v>24.722472814977049</v>
+        <v>26.96182240758241</v>
       </c>
       <c r="BZ4">
-        <v>23.634510410909936</v>
+        <v>22.587087991653622</v>
       </c>
       <c r="CA4">
-        <v>-39.4321280414822</v>
+        <v>-48.0268771185745</v>
       </c>
       <c r="CB4">
-        <v>61.657272904536171</v>
+        <v>60.609875992524017</v>
       </c>
       <c r="CC4">
-        <v>24.727364068804444</v>
+        <v>26.967002730801205</v>
       </c>
       <c r="CD4">
-        <v>3.4059242341960627</v>
+        <v>3.4647818785490112</v>
       </c>
       <c r="CE4">
-        <v>8.4926156874493479</v>
+        <v>7.787294794914005</v>
       </c>
     </row>
     <row r="5" spans="1:83">
@@ -3297,7 +3297,7 @@
         <v>221.56851216319822</v>
       </c>
       <c r="G5">
-        <v>222.7421977429814</v>
+        <v>185.61849811915121</v>
       </c>
       <c r="H5">
         <v>8833323.1312651373</v>
@@ -3306,7 +3306,7 @@
         <v>39867231336368.211</v>
       </c>
       <c r="J5">
-        <v>166.48888186767266</v>
+        <v>165.28254301559932</v>
       </c>
       <c r="K5">
         <v>181.62685749265097</v>
@@ -3315,7 +3315,7 @@
         <v>198.28425061834395</v>
       </c>
       <c r="M5">
-        <v>1.7105297219569222</v>
+        <v>1.7016626849660006</v>
       </c>
       <c r="N5">
         <v>1.8052198486722362</v>
@@ -3324,7 +3324,7 @@
         <v>1.9221548222195981</v>
       </c>
       <c r="P5">
-        <v>1.7105297219569222</v>
+        <v>1.7016626849660006</v>
       </c>
       <c r="Q5">
         <v>1.8052198486722362</v>
@@ -3342,7 +3342,7 @@
         <v>56.148773165138714</v>
       </c>
       <c r="V5">
-        <v>35.143874297832284</v>
+        <v>51.470815454060336</v>
       </c>
       <c r="W5">
         <v>137.75453774880765</v>
@@ -3357,31 +3357,31 @@
         <v>32.176240822764612</v>
       </c>
       <c r="AA5">
-        <v>2.3918340276964503</v>
+        <v>2.1945333115576586</v>
       </c>
       <c r="AB5">
-        <v>4.0130677606868312</v>
+        <v>4.0130677606868321</v>
       </c>
       <c r="AC5">
-        <v>0.49851220045628508</v>
+        <v>0.45745037985418258</v>
       </c>
       <c r="AD5">
-        <v>1.02112476312549</v>
+        <v>1.0199174432371907</v>
       </c>
       <c r="AE5">
-        <v>282.02934484233856</v>
+        <v>263.31383652647094</v>
       </c>
       <c r="AF5">
-        <v>578.6854188569157</v>
+        <v>419.24412577602948</v>
       </c>
       <c r="AG5">
-        <v>95627.555026094589</v>
+        <v>95626.416122573442</v>
       </c>
       <c r="AH5">
-        <v>64444.319346376462</v>
+        <v>53703.579466468676</v>
       </c>
       <c r="AI5">
-        <v>64444.319346376462</v>
+        <v>53703.579466468676</v>
       </c>
       <c r="AJ5">
         <v>30.459331850556751</v>
@@ -3396,136 +3396,136 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>-8.8648679131549653</v>
+        <v>-8.8616314733759367</v>
       </c>
       <c r="AO5">
-        <v>-7.31088460352096</v>
+        <v>-7.3108027720963227</v>
       </c>
       <c r="AP5">
-        <v>-2.3147922448954281</v>
+        <v>-2.1238503535501496</v>
       </c>
       <c r="AQ5">
-        <v>-3.8833968639683865</v>
+        <v>-3.8835509159257886</v>
       </c>
       <c r="AR5">
-        <v>2007.1972781970289</v>
+        <v>2007.1795538431666</v>
       </c>
       <c r="AS5">
-        <v>1655.6141617875069</v>
+        <v>1378.0740145548966</v>
       </c>
       <c r="AT5">
-        <v>-0.78276848512284647</v>
+        <v>-0.85993716902044781</v>
       </c>
       <c r="AU5">
         <v>-0.73474148700123421</v>
       </c>
       <c r="AV5">
-        <v>-0.56339752583343394</v>
+        <v>-0.45545012743149016</v>
       </c>
       <c r="AW5">
         <v>0.48206945464480805</v>
       </c>
       <c r="AX5">
-        <v>1.3617062861114033</v>
+        <v>1.1497984654533422</v>
       </c>
       <c r="AY5">
         <v>1.6632291046720036</v>
       </c>
       <c r="AZ5">
-        <v>-2.6940218963356477</v>
+        <v>-2.8362113105133644</v>
       </c>
       <c r="BA5">
         <v>2.9873114838301436</v>
       </c>
       <c r="BB5">
-        <v>-0.42313760685437457</v>
+        <v>-0.45496284144634641</v>
       </c>
       <c r="BC5">
-        <v>-0.31624550630632275</v>
+        <v>-0.26094876267495082</v>
       </c>
       <c r="BD5">
-        <v>-0.25609156732503241</v>
+        <v>-0.19831678011062234</v>
       </c>
       <c r="BE5">
-        <v>-0.51719249093503372</v>
+        <v>-0.51719773800219471</v>
       </c>
       <c r="BF5">
-        <v>-127586645372.03212</v>
+        <v>-98803706788.913452</v>
       </c>
       <c r="BG5">
-        <v>-312387090465.95715</v>
+        <v>-375304760513.34894</v>
       </c>
       <c r="BH5">
-        <v>61.600770618727644</v>
+        <v>61.175435595217323</v>
       </c>
       <c r="BI5">
         <v>45.475952674809562</v>
       </c>
       <c r="BJ5">
-        <v>-1.722165385267773</v>
+        <v>-1.9304533297778792</v>
       </c>
       <c r="BK5">
         <v>3.2960927582525379</v>
       </c>
       <c r="BL5">
-        <v>-2.4791418622895973</v>
+        <v>-2.3747591563340258</v>
       </c>
       <c r="BM5">
         <v>0.90891885503969294</v>
       </c>
       <c r="BN5">
-        <v>0.24325276893087511</v>
+        <v>0.19407832565163055</v>
       </c>
       <c r="BO5">
-        <v>0.14187482242058624</v>
+        <v>0.12334211808026455</v>
       </c>
       <c r="BP5">
-        <v>-0.811904805846927</v>
+        <v>-0.81563452605423681</v>
       </c>
       <c r="BQ5">
-        <v>2.0271016565768369</v>
+        <v>1.9784924052732231</v>
       </c>
       <c r="BR5">
-        <v>39.492682619161627</v>
+        <v>39.498416728722219</v>
       </c>
       <c r="BS5">
-        <v>-2.4922680161524715</v>
+        <v>-2.2666835843557211</v>
       </c>
       <c r="BT5">
-        <v>-0.02674359702729923</v>
+        <v>-0.031241039556704375</v>
       </c>
       <c r="BU5">
-        <v>1.8113009368199287</v>
+        <v>1.6171974691836029</v>
       </c>
       <c r="BV5">
-        <v>21.333706842884123</v>
+        <v>21.334611665938009</v>
       </c>
       <c r="BW5">
-        <v>-2.629940464205033</v>
+        <v>-2.6225902400118373</v>
       </c>
       <c r="BX5">
-        <v>-12.399208434351369</v>
+        <v>-14.525331391123771</v>
       </c>
       <c r="BY5">
-        <v>10.31723624050465</v>
+        <v>12.714917664644874</v>
       </c>
       <c r="BZ5">
-        <v>16.242467757309381</v>
+        <v>17.598807113973834</v>
       </c>
       <c r="CA5">
-        <v>-15.280578534473921</v>
+        <v>-20.979858600936083</v>
       </c>
       <c r="CB5">
-        <v>56.1098441517629</v>
+        <v>57.466123388903355</v>
       </c>
       <c r="CC5">
-        <v>10.321964412681934</v>
+        <v>12.720455372429175</v>
       </c>
       <c r="CD5">
-        <v>3.7426587646902609</v>
+        <v>3.6543268906242381</v>
       </c>
       <c r="CE5">
-        <v>20.344964543957008</v>
+        <v>16.508842950320979</v>
       </c>
     </row>
   </sheetData>
@@ -4392,7 +4392,7 @@
         <v>143.00704677873924</v>
       </c>
       <c r="G3">
-        <v>104.53435477471319</v>
+        <v>91.467560427874034</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -4401,31 +4401,31 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>97.126137383957371</v>
+        <v>96.083986569790866</v>
       </c>
       <c r="K3">
         <v>114.95586765629335</v>
       </c>
       <c r="L3">
-        <v>126.37845105399929</v>
+        <v>126.98694743576179</v>
       </c>
       <c r="M3">
-        <v>1.1879899905508486</v>
+        <v>1.1788798183979889</v>
       </c>
       <c r="N3">
         <v>1.3257281201909439</v>
       </c>
       <c r="O3">
-        <v>1.4185041038211952</v>
+        <v>1.4233774521633402</v>
       </c>
       <c r="P3">
-        <v>1.1879899905508486</v>
+        <v>1.1788798183979889</v>
       </c>
       <c r="Q3">
         <v>1.3257281201909439</v>
       </c>
       <c r="R3">
-        <v>1.4185041038211952</v>
+        <v>1.4233774521633402</v>
       </c>
       <c r="S3">
         <v>83.441196534470748</v>
@@ -4437,46 +4437,46 @@
         <v>71.142607476102043</v>
       </c>
       <c r="V3">
-        <v>5.1091309723327304E-15</v>
+        <v>41.967078641242033</v>
       </c>
       <c r="W3">
         <v>135.62894802063056</v>
       </c>
       <c r="X3">
-        <v>47.901699647906668</v>
+        <v>37.922323195539839</v>
       </c>
       <c r="Y3">
         <v>36.460932396303264</v>
       </c>
       <c r="Z3">
-        <v>19.08948476405914</v>
+        <v>19.089484764059137</v>
       </c>
       <c r="AA3">
-        <v>1.4036540079488462</v>
+        <v>1.0465943133076889</v>
       </c>
       <c r="AB3">
-        <v>2.1463435048803872</v>
+        <v>2.1463435048803867</v>
       </c>
       <c r="AC3">
-        <v>0.31528382193045834</v>
+        <v>0.23511685094091103</v>
       </c>
       <c r="AD3">
-        <v>0.923784490912283</v>
+        <v>0.92229276830267226</v>
       </c>
       <c r="AE3">
-        <v>77.481654090600728</v>
+        <v>65.736417012307314</v>
       </c>
       <c r="AF3">
-        <v>117.29049494700097</v>
+        <v>87.729241455364473</v>
       </c>
       <c r="AG3">
-        <v>53113.012314973814</v>
+        <v>53112.299665345869</v>
       </c>
       <c r="AH3">
-        <v>10646.479950223296</v>
+        <v>9315.6660887352373</v>
       </c>
       <c r="AI3">
-        <v>10646.479950223296</v>
+        <v>9315.6660887352373</v>
       </c>
       <c r="AJ3">
         <v>28.256244458071322</v>
@@ -4491,136 +4491,136 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-8.212287624087617</v>
+        <v>-8.2089136118429344</v>
       </c>
       <c r="AO3">
-        <v>-4.3296920398332315</v>
+        <v>-4.3296379676785781</v>
       </c>
       <c r="AP3">
-        <v>-1.3584847135897169</v>
+        <v>-1.0129171405976398</v>
       </c>
       <c r="AQ3">
-        <v>-2.076808485306846</v>
+        <v>-2.0769212101747749</v>
       </c>
       <c r="AR3">
-        <v>1200.866149310031</v>
+        <v>1200.8526725638205</v>
       </c>
       <c r="AS3">
-        <v>462.40518694834083</v>
+        <v>403.96427978050838</v>
       </c>
       <c r="AT3">
-        <v>-0.86629037324735392</v>
+        <v>-0.89147065040703544</v>
       </c>
       <c r="AU3">
-        <v>-0.29093264423557008</v>
+        <v>-0.30695838995491465</v>
       </c>
       <c r="AV3">
-        <v>-0.685685911796377</v>
+        <v>-0.45542786495666443</v>
       </c>
       <c r="AW3">
-        <v>0.22950193039629441</v>
+        <v>0.25560882651412148</v>
       </c>
       <c r="AX3">
         <v>0</v>
       </c>
       <c r="AY3">
-        <v>1.9125761429421631</v>
+        <v>1.9548863602786866</v>
       </c>
       <c r="AZ3">
         <v>0</v>
       </c>
       <c r="BA3">
-        <v>2.8478836223603206</v>
+        <v>2.8749216546681868</v>
       </c>
       <c r="BB3">
-        <v>-0.97672525335339744</v>
+        <v>-1.020686850826547</v>
       </c>
       <c r="BC3">
-        <v>-1.1325889348842637</v>
+        <v>-0.751357096307792</v>
       </c>
       <c r="BD3">
         <v>0</v>
       </c>
       <c r="BE3">
-        <v>-0.19958752616448802</v>
+        <v>-0.20672198956566651</v>
       </c>
       <c r="BF3">
         <v>0</v>
       </c>
       <c r="BG3">
-        <v>-431629081588.96936</v>
+        <v>-511733338596.14441</v>
       </c>
       <c r="BH3">
-        <v>65.893711262009532</v>
+        <v>65.080063215132057</v>
       </c>
       <c r="BI3">
-        <v>41.6441595007797</v>
+        <v>41.88964317201048</v>
       </c>
       <c r="BJ3">
         <v>0</v>
       </c>
       <c r="BK3">
-        <v>3.3216670862229325</v>
+        <v>3.3748599009977873</v>
       </c>
       <c r="BL3">
         <v>0</v>
       </c>
       <c r="BM3">
-        <v>0.85727265053943835</v>
+        <v>0.8349106842776175</v>
       </c>
       <c r="BN3">
         <v>90</v>
       </c>
       <c r="BO3">
-        <v>0.16290751013899982</v>
+        <v>0.13348626377287912</v>
       </c>
       <c r="BP3">
-        <v>-1.2029987098690516</v>
+        <v>-0.89696618177351106</v>
       </c>
       <c r="BQ3">
-        <v>36.468104281493453</v>
+        <v>36.464920163538</v>
       </c>
       <c r="BR3">
-        <v>-1.6472444347854445</v>
+        <v>-1.2282546355569406</v>
       </c>
       <c r="BS3">
-        <v>-44.262800453951812</v>
+        <v>-44.266527127019323</v>
       </c>
       <c r="BT3">
-        <v>-0.44764546574050673</v>
+        <v>-0.030025840697198547</v>
       </c>
       <c r="BU3">
-        <v>2.3174699535013916</v>
+        <v>2.1065286208065608</v>
       </c>
       <c r="BV3">
-        <v>23.13375076186183</v>
+        <v>23.135142381870498</v>
       </c>
       <c r="BW3">
-        <v>-2.5855451171851036</v>
+        <v>-2.5730633174334874</v>
       </c>
       <c r="BX3">
         <v>0</v>
       </c>
       <c r="BY3">
-        <v>65.666799577869369</v>
+        <v>81.0388296790727</v>
       </c>
       <c r="BZ3">
         <v>0</v>
       </c>
       <c r="CA3">
-        <v>-75.085412563794421</v>
+        <v>-101.05675412475063</v>
       </c>
       <c r="CB3">
         <v>0</v>
       </c>
       <c r="CC3">
-        <v>65.668218115494341</v>
+        <v>81.040445376142813</v>
       </c>
       <c r="CD3">
         <v>1E+307</v>
       </c>
       <c r="CE3">
-        <v>3.1978939893063849</v>
+        <v>2.5912986907377129</v>
       </c>
     </row>
     <row r="4" spans="1:83">
@@ -4643,7 +4643,7 @@
         <v>163.2443505702883</v>
       </c>
       <c r="G4">
-        <v>168.94859367331856</v>
+        <v>147.83001946415376</v>
       </c>
       <c r="H4">
         <v>581099.64567733079</v>
@@ -4652,31 +4652,31 @@
         <v>3559692226084.8848</v>
       </c>
       <c r="J4">
-        <v>126.37845105399929</v>
+        <v>126.98694743576179</v>
       </c>
       <c r="K4">
         <v>151.02434149969008</v>
       </c>
       <c r="L4">
-        <v>166.48888186767266</v>
+        <v>165.79407761584392</v>
       </c>
       <c r="M4">
-        <v>1.4185041038211952</v>
+        <v>1.4233774521633402</v>
       </c>
       <c r="N4">
         <v>1.59540942006844</v>
       </c>
       <c r="O4">
-        <v>1.7105297219569222</v>
+        <v>1.7054249007640661</v>
       </c>
       <c r="P4">
-        <v>1.4185041038211952</v>
+        <v>1.4233774521633402</v>
       </c>
       <c r="Q4">
         <v>1.59540942006844</v>
       </c>
       <c r="R4">
-        <v>1.7105297219569222</v>
+        <v>1.7054249007640661</v>
       </c>
       <c r="S4">
         <v>71.142607476102043</v>
@@ -4688,13 +4688,13 @@
         <v>61.0312751794986</v>
       </c>
       <c r="V4">
-        <v>47.901699647906668</v>
+        <v>37.922323195539839</v>
       </c>
       <c r="W4">
         <v>138.98989389998002</v>
       </c>
       <c r="X4">
-        <v>35.143874297832284</v>
+        <v>45.262469984140928</v>
       </c>
       <c r="Y4">
         <v>38.955441574532315</v>
@@ -4703,31 +4703,31 @@
         <v>24.268446449383816</v>
       </c>
       <c r="AA4">
-        <v>1.2347859788971805</v>
+        <v>1.3275494685442875</v>
       </c>
       <c r="AB4">
-        <v>3.420104345506259</v>
+        <v>3.4198835837585326</v>
       </c>
       <c r="AC4">
-        <v>0.25962063569928129</v>
+        <v>0.27911492408533461</v>
       </c>
       <c r="AD4">
-        <v>1.1539778912488536</v>
+        <v>1.1540064426669374</v>
       </c>
       <c r="AE4">
-        <v>89.864418992600932</v>
+        <v>93.507594951295388</v>
       </c>
       <c r="AF4">
-        <v>371.0599104135274</v>
+        <v>285.95409609648021</v>
       </c>
       <c r="AG4">
-        <v>69208.295269758208</v>
+        <v>69208.516307121958</v>
       </c>
       <c r="AH4">
-        <v>27813.733635940083</v>
+        <v>24337.033126595481</v>
       </c>
       <c r="AI4">
-        <v>27813.733635940083</v>
+        <v>24337.033126595481</v>
       </c>
       <c r="AJ4">
         <v>30.189422150205413</v>
@@ -4742,136 +4742,136 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-8.7715245183062187</v>
+        <v>-8.7723825078705922</v>
       </c>
       <c r="AO4">
-        <v>-5.5288225981092314</v>
+        <v>-5.528819801142081</v>
       </c>
       <c r="AP4">
-        <v>-1.1950525453345111</v>
+        <v>-1.2848304459012616</v>
       </c>
       <c r="AQ4">
-        <v>-3.3094286502204304</v>
+        <v>-3.3092051781466614</v>
       </c>
       <c r="AR4">
-        <v>1464.576851344719</v>
+        <v>1464.5807754706079</v>
       </c>
       <c r="AS4">
-        <v>950.10957599272524</v>
+        <v>830.04177351674593</v>
       </c>
       <c r="AT4">
-        <v>-1.2877052060656851</v>
+        <v>-1.2574550857755988</v>
       </c>
       <c r="AU4">
-        <v>-0.52270467107163288</v>
+        <v>-0.50109085534157694</v>
       </c>
       <c r="AV4">
-        <v>-0.49058764862043963</v>
+        <v>-0.54178548216380717</v>
       </c>
       <c r="AW4">
-        <v>0.38263408860820797</v>
+        <v>0.34898919326555422</v>
       </c>
       <c r="AX4">
-        <v>0.0063881292392773117</v>
+        <v>0.0070813367200935036</v>
       </c>
       <c r="AY4">
-        <v>3.4281848436220357</v>
+        <v>2.9484091064277504</v>
       </c>
       <c r="AZ4">
-        <v>-0.017107298644921835</v>
+        <v>-0.016698846201012481</v>
       </c>
       <c r="BA4">
-        <v>5.6329798166819831</v>
+        <v>5.2685939096780379</v>
       </c>
       <c r="BB4">
-        <v>-1.2653413892150158</v>
+        <v>-1.2406030350005852</v>
       </c>
       <c r="BC4">
-        <v>-0.70508540885204973</v>
+        <v>-0.7554194641748061</v>
       </c>
       <c r="BD4">
-        <v>-0.014250198635767897</v>
+        <v>-0.016215099563191903</v>
       </c>
       <c r="BE4">
-        <v>-0.49866663652641835</v>
+        <v>-0.4518125363571171</v>
       </c>
       <c r="BF4">
-        <v>-9729908418.7244282</v>
+        <v>-11071495567.037994</v>
       </c>
       <c r="BG4">
-        <v>-524851710925.4317</v>
+        <v>-544325057813.49316</v>
       </c>
       <c r="BH4">
-        <v>66.761753096516145</v>
+        <v>66.956303527021433</v>
       </c>
       <c r="BI4">
-        <v>40.393841084073159</v>
+        <v>40.037774009589732</v>
       </c>
       <c r="BJ4">
-        <v>-0.013198949802919493</v>
+        <v>-0.012594519288610464</v>
       </c>
       <c r="BK4">
-        <v>6.26131808834377</v>
+        <v>5.646609443442177</v>
       </c>
       <c r="BL4">
-        <v>-0.012619650795654594</v>
+        <v>-0.013052772811829393</v>
       </c>
       <c r="BM4">
-        <v>2.0685281563869387</v>
+        <v>2.1370540089553716</v>
       </c>
       <c r="BN4">
-        <v>0.071131175937274776</v>
+        <v>0.080228907757520632</v>
       </c>
       <c r="BO4">
-        <v>0.252522589350759</v>
+        <v>0.25478637878185012</v>
       </c>
       <c r="BP4">
-        <v>-0.92985205240689917</v>
+        <v>-0.92891864570344829</v>
       </c>
       <c r="BQ4">
-        <v>1.5521305690662293</v>
+        <v>1.5779043190397581</v>
       </c>
       <c r="BR4">
-        <v>44.26378540144767</v>
+        <v>44.262531106397105</v>
       </c>
       <c r="BS4">
-        <v>-1.4112605474165583</v>
+        <v>-1.5201707795445665</v>
       </c>
       <c r="BT4">
-        <v>-0.00816353908432399</v>
+        <v>-0.013234116188784536</v>
       </c>
       <c r="BU4">
-        <v>2.4718928885061073</v>
+        <v>2.2616923994097351</v>
       </c>
       <c r="BV4">
-        <v>23.105608349902166</v>
+        <v>23.105482237078888</v>
       </c>
       <c r="BW4">
-        <v>-3.2583661824327308</v>
+        <v>-3.25911701167518</v>
       </c>
       <c r="BX4">
-        <v>-0.22814068565492474</v>
+        <v>-0.21270281227422822</v>
       </c>
       <c r="BY4">
-        <v>41.711681865740886</v>
+        <v>44.661804610359958</v>
       </c>
       <c r="BZ4">
-        <v>0.21535186471895582</v>
+        <v>0.21309944188072361</v>
       </c>
       <c r="CA4">
-        <v>-56.700519133690989</v>
+        <v>-66.385257071026217</v>
       </c>
       <c r="CB4">
-        <v>3.7750566298574686</v>
+        <v>3.7728079129323304</v>
       </c>
       <c r="CC4">
-        <v>41.714983799436368</v>
+        <v>44.665121524770683</v>
       </c>
       <c r="CD4">
-        <v>55.628304576699492</v>
+        <v>55.661460865836183</v>
       </c>
       <c r="CE4">
-        <v>5.0341623290487147</v>
+        <v>4.7016551803970081</v>
       </c>
     </row>
     <row r="5" spans="1:83">
@@ -4894,7 +4894,7 @@
         <v>207.90056424220626</v>
       </c>
       <c r="G5">
-        <v>348.25126511214194</v>
+        <v>304.71985697312419</v>
       </c>
       <c r="H5">
         <v>1357619.2148630719</v>
@@ -4903,7 +4903,7 @@
         <v>6530137230803.4326</v>
       </c>
       <c r="J5">
-        <v>166.48888186767266</v>
+        <v>165.79407761584392</v>
       </c>
       <c r="K5">
         <v>185.8156494414562</v>
@@ -4912,7 +4912,7 @@
         <v>198.62630079567148</v>
       </c>
       <c r="M5">
-        <v>1.7105297219569222</v>
+        <v>1.7054249007640661</v>
       </c>
       <c r="N5">
         <v>1.8349026521330976</v>
@@ -4921,7 +4921,7 @@
         <v>1.9245259978055951</v>
       </c>
       <c r="P5">
-        <v>1.7105297219569222</v>
+        <v>1.7054249007640661</v>
       </c>
       <c r="Q5">
         <v>1.8349026521330976</v>
@@ -4939,7 +4939,7 @@
         <v>56.148773165138714</v>
       </c>
       <c r="V5">
-        <v>35.143874297832284</v>
+        <v>45.262469984140928</v>
       </c>
       <c r="W5">
         <v>119.88885722682392</v>
@@ -4954,31 +4954,31 @@
         <v>34.842638625968164</v>
       </c>
       <c r="AA5">
-        <v>1.303803405084178</v>
+        <v>1.2042257963696805</v>
       </c>
       <c r="AB5">
-        <v>4.4528897555005962</v>
+        <v>4.4528897555005953</v>
       </c>
       <c r="AC5">
-        <v>0.24291984584026707</v>
+        <v>0.22437337557496775</v>
       </c>
       <c r="AD5">
-        <v>1.0491275514366969</v>
+        <v>1.0474315843388802</v>
       </c>
       <c r="AE5">
-        <v>141.03155866119</v>
+        <v>136.15326011675421</v>
       </c>
       <c r="AF5">
-        <v>1443.4246946843782</v>
+        <v>1097.6408883363754</v>
       </c>
       <c r="AG5">
-        <v>112251.4755067729</v>
+        <v>112251.17960769903</v>
       </c>
       <c r="AH5">
-        <v>118169.53958632483</v>
+        <v>103398.29177436832</v>
       </c>
       <c r="AI5">
-        <v>118169.53958632483</v>
+        <v>103398.29177436832</v>
       </c>
       <c r="AJ5">
         <v>34.069326956572112</v>
@@ -4993,136 +4993,136 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>-9.8980555781374342</v>
+        <v>-9.89725665238837</v>
       </c>
       <c r="AO5">
-        <v>-7.9207451709114896</v>
+        <v>-7.9206176324062172</v>
       </c>
       <c r="AP5">
-        <v>-1.2618495796676634</v>
+        <v>-1.1654766389303171</v>
       </c>
       <c r="AQ5">
-        <v>-4.3085855105818975</v>
+        <v>-4.3088199644136562</v>
       </c>
       <c r="AR5">
-        <v>2104.9291922118787</v>
+        <v>2104.9244835726263</v>
       </c>
       <c r="AS5">
-        <v>2811.7800260485265</v>
+        <v>2456.4191518072284</v>
       </c>
       <c r="AT5">
-        <v>-1.1525524014398942</v>
+        <v>-1.203643199342477</v>
       </c>
       <c r="AU5">
         <v>-0.64529803603695657</v>
       </c>
       <c r="AV5">
-        <v>-0.53464256239671415</v>
+        <v>-0.45709586679797082</v>
       </c>
       <c r="AW5">
         <v>0.49067396749505227</v>
       </c>
       <c r="AX5">
-        <v>0.025589715093421096</v>
+        <v>0.022004557564488172</v>
       </c>
       <c r="AY5">
         <v>5.005504086589454</v>
       </c>
       <c r="AZ5">
-        <v>-0.057469560337644769</v>
+        <v>-0.059816099216522</v>
       </c>
       <c r="BA5">
         <v>8.50379768145403</v>
       </c>
       <c r="BB5">
-        <v>-0.93968543284569273</v>
+        <v>-0.99769907736670815</v>
       </c>
       <c r="BC5">
-        <v>-0.650965745442545</v>
+        <v>-0.54333888329636926</v>
       </c>
       <c r="BD5">
-        <v>-0.0379839879298231</v>
+        <v>-0.031121708548823269</v>
       </c>
       <c r="BE5">
-        <v>-0.91578995462086965</v>
+        <v>-0.91580017904761979</v>
       </c>
       <c r="BF5">
-        <v>-18045256852.516346</v>
+        <v>-14785190058.695744</v>
       </c>
       <c r="BG5">
-        <v>-325697581651.81042</v>
+        <v>-372819182090.25946</v>
       </c>
       <c r="BH5">
-        <v>69.480425342817583</v>
+        <v>69.2992570616647</v>
       </c>
       <c r="BI5">
         <v>41.9924343736633</v>
       </c>
       <c r="BJ5">
-        <v>-0.044853364304879455</v>
+        <v>-0.048176014338982873</v>
       </c>
       <c r="BK5">
         <v>9.4095734751608049</v>
       </c>
       <c r="BL5">
-        <v>-0.044110765063626156</v>
+        <v>-0.041728143039198307</v>
       </c>
       <c r="BM5">
         <v>2.97145977316148</v>
       </c>
       <c r="BN5">
-        <v>0.070793963145915711</v>
+        <v>0.060194636309044765</v>
       </c>
       <c r="BO5">
-        <v>0.22100850335096672</v>
+        <v>0.19207367046695797</v>
       </c>
       <c r="BP5">
-        <v>-0.93043232535999909</v>
+        <v>-0.93133024604553283</v>
       </c>
       <c r="BQ5">
-        <v>1.5301645587932762</v>
+        <v>1.5055982500186464</v>
       </c>
       <c r="BR5">
-        <v>44.264610334633218</v>
+        <v>-28.39422745404524</v>
       </c>
       <c r="BS5">
-        <v>-1.3237241847788033</v>
+        <v>-1.2397851487090015</v>
       </c>
       <c r="BT5">
-        <v>-0.43839579520121663</v>
+        <v>-0.02145318543501621</v>
       </c>
       <c r="BU5">
-        <v>2.4013179948256735</v>
+        <v>2.1906217761344191</v>
       </c>
       <c r="BV5">
-        <v>23.118852856437286</v>
+        <v>23.120428154731275</v>
       </c>
       <c r="BW5">
-        <v>-2.9528200124335933</v>
+        <v>-2.9404600601497908</v>
       </c>
       <c r="BX5">
-        <v>-0.48701577071451324</v>
+        <v>-0.53308206269307779</v>
       </c>
       <c r="BY5">
-        <v>15.665029283996853</v>
+        <v>18.779815417913316</v>
       </c>
       <c r="BZ5">
-        <v>0.43838869451619128</v>
+        <v>0.42812618969706778</v>
       </c>
       <c r="CA5">
-        <v>-19.830544835437887</v>
+        <v>-25.871654455282677</v>
       </c>
       <c r="CB5">
-        <v>6.96854928971207</v>
+        <v>6.9582791285576064</v>
       </c>
       <c r="CC5">
-        <v>15.668414769311312</v>
+        <v>18.783515679271257</v>
       </c>
       <c r="CD5">
-        <v>30.135397091907041</v>
+        <v>30.179875817015585</v>
       </c>
       <c r="CE5">
-        <v>13.402759825538515</v>
+        <v>11.180015689594661</v>
       </c>
     </row>
   </sheetData>
